--- a/output/topology_excel/8428.xlsx
+++ b/output/topology_excel/8428.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         <v>6</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,46 +748,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>157</v>
+        <v>240</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -795,21 +795,21 @@
         <v>1</v>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="F17" t="n">
-        <v>114</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -817,461 +817,197 @@
         <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>116</v>
+        <v>245</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>178</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
         <v>2</v>
       </c>
-      <c r="B20" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>202</v>
-      </c>
       <c r="F20" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
         <v>2</v>
       </c>
-      <c r="B21" t="n">
-        <v>7</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>100</v>
-      </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
         <v>3</v>
       </c>
-      <c r="B22" t="n">
-        <v>7</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>252</v>
-      </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>190</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>164</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>296</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B26" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>6</v>
-      </c>
-      <c r="B27" t="n">
-        <v>11</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
-        <v>407</v>
-      </c>
-      <c r="F27" t="n">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>6</v>
-      </c>
-      <c r="B28" t="n">
-        <v>13</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>307</v>
-      </c>
-      <c r="F28" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>6</v>
-      </c>
-      <c r="B29" t="n">
-        <v>14</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>328</v>
-      </c>
-      <c r="F29" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>6</v>
-      </c>
-      <c r="B30" t="n">
-        <v>15</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>127</v>
-      </c>
-      <c r="F30" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>8</v>
-      </c>
-      <c r="B31" t="n">
-        <v>9</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>164</v>
-      </c>
-      <c r="F31" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>9</v>
-      </c>
-      <c r="B32" t="n">
-        <v>10</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="n">
-        <v>369</v>
-      </c>
-      <c r="F32" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>10</v>
-      </c>
-      <c r="B33" t="n">
-        <v>11</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="n">
-        <v>142</v>
-      </c>
-      <c r="F33" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>10</v>
-      </c>
-      <c r="B34" t="n">
-        <v>12</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="n">
-        <v>369</v>
-      </c>
-      <c r="F34" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>11</v>
-      </c>
-      <c r="B35" t="n">
-        <v>12</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="n">
-        <v>236</v>
-      </c>
-      <c r="F35" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>11</v>
-      </c>
-      <c r="B36" t="n">
-        <v>13</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="n">
-        <v>158</v>
-      </c>
-      <c r="F36" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>12</v>
-      </c>
-      <c r="B37" t="n">
-        <v>13</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="n">
-        <v>295</v>
-      </c>
-      <c r="F37" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>14</v>
-      </c>
-      <c r="B38" t="n">
-        <v>15</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="n">
-        <v>127</v>
-      </c>
-      <c r="F38" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/8428.xlsx
+++ b/output/topology_excel/8428.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,82 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Length_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Width_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Length_6</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Width_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Length_7</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Width_7</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Length_8</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Width_8</t>
         </is>
       </c>
     </row>
@@ -481,6 +551,20 @@
       <c r="F2" t="n">
         <v>13</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +587,20 @@
       <c r="F3" t="n">
         <v>19</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +623,20 @@
       <c r="F4" t="n">
         <v>14</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +659,20 @@
       <c r="F5" t="n">
         <v>13</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +695,20 @@
       <c r="F6" t="n">
         <v>13</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +731,20 @@
       <c r="F7" t="n">
         <v>12</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +767,20 @@
       <c r="F8" t="n">
         <v>12</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +803,20 @@
       <c r="F9" t="n">
         <v>15</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +839,20 @@
       <c r="F10" t="n">
         <v>15</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +875,20 @@
       <c r="F11" t="n">
         <v>12</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +911,20 @@
       <c r="F12" t="n">
         <v>12</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +947,20 @@
       <c r="F13" t="n">
         <v>12</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +983,20 @@
       <c r="F14" t="n">
         <v>12</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +1019,20 @@
       <c r="F15" t="n">
         <v>1</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +1055,20 @@
       <c r="F16" t="n">
         <v>1</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +1091,20 @@
       <c r="F17" t="n">
         <v>1</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +1127,20 @@
       <c r="F18" t="n">
         <v>1</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -847,7 +1155,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -855,158 +1163,46 @@
       <c r="F19" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" t="n">
-        <v>19</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="G19" t="n">
         <v>2</v>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B21" t="n">
-        <v>19</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
         <v>2</v>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>11</v>
-      </c>
-      <c r="B22" t="n">
-        <v>19</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
         <v>3</v>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>11</v>
-      </c>
-      <c r="B23" t="n">
-        <v>19</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
         <v>2</v>
       </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>11</v>
-      </c>
-      <c r="B24" t="n">
-        <v>19</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
         <v>3</v>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>11</v>
-      </c>
-      <c r="B25" t="n">
-        <v>19</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>11</v>
-      </c>
-      <c r="B26" t="n">
-        <v>19</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
         <v>1</v>
       </c>
     </row>
